--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486804_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486804_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2386</v>
+        <v>8.126899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.052</v>
+        <v>7.4867</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1866</v>
+        <v>0.6403</v>
       </c>
       <c r="G2" t="n">
         <v>4.0488</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1319</v>
+        <v>3.0202</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4818</v>
+        <v>1.9164</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6501</v>
+        <v>1.1038</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3334</v>
+        <v>5.1029</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6614</v>
+        <v>6.2819</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.328</v>
+        <v>-1.179</v>
       </c>
       <c r="G3" t="n">
         <v>3.775</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2648</v>
+        <v>1.0343</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3307</v>
+        <v>0.9513</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.066</v>
+        <v>0.083</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>A. TORRES MUNICIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4515</v>
+        <v>3.2403</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6341</v>
+        <v>2.1102</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1825</v>
+        <v>1.1302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3307</v>
+        <v>3.7161</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8348</v>
+        <v>2.1381</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5041</v>
+        <v>1.578</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8896</v>
+        <v>4.2826</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3177</v>
+        <v>1.3797</v>
       </c>
       <c r="L4" t="n">
-        <v>0.572</v>
+        <v>2.9029</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.559</v>
+        <v>-0.5665</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4829</v>
+        <v>0.7583</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0761</v>
+        <v>-1.3248</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3862</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7926</v>
+        <v>1.2619</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5167</v>
+        <v>0.7237</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2759</v>
+        <v>0.5382</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7615</v>
+        <v>2.9353</v>
       </c>
       <c r="E5" t="n">
         <v>2.0767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6848</v>
+        <v>0.8586</v>
       </c>
       <c r="G5" t="n">
         <v>2.6554</v>
@@ -844,13 +844,13 @@
         <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9709</v>
+        <v>1.1447</v>
       </c>
       <c r="T5" t="n">
         <v>0.4688</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5022</v>
+        <v>0.676</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2856</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TORRES MUNICIO</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3867</v>
+        <v>2.9344</v>
       </c>
       <c r="E6" t="n">
-        <v>1.331</v>
+        <v>4.117</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0557</v>
+        <v>-1.1825</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7161</v>
+        <v>0.3307</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1381</v>
+        <v>0.8348</v>
       </c>
       <c r="I6" t="n">
-        <v>1.578</v>
+        <v>-0.5041</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2826</v>
+        <v>1.8896</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3797</v>
+        <v>1.3177</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9029</v>
+        <v>0.572</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5665</v>
+        <v>-1.559</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7583</v>
+        <v>-0.4829</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3248</v>
+        <v>-1.0761</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4083</v>
+        <v>1.2755</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0554</v>
+        <v>0.9996</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4637</v>
+        <v>0.2759</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2575</v>
+        <v>2.6767</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6363</v>
+        <v>2.1052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6211</v>
+        <v>0.5715</v>
       </c>
       <c r="G7" t="n">
         <v>1.118</v>
@@ -1000,13 +1000,13 @@
         <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4911</v>
+        <v>0.9103</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2204</v>
+        <v>0.6892</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2707</v>
+        <v>0.221</v>
       </c>
       <c r="V7" t="n">
         <v>1.2277</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.827</v>
+        <v>1.6035</v>
       </c>
       <c r="E8" t="n">
-        <v>2.084</v>
+        <v>1.5421</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.257</v>
+        <v>0.0613</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1363</v>
+        <v>-0.7894</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5998</v>
+        <v>1.4622</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4634</v>
+        <v>-2.2516</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5911</v>
+        <v>0.8183</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.634</v>
+        <v>1.4625</v>
       </c>
       <c r="L8" t="n">
-        <v>0.043</v>
+        <v>-0.6442</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5453</v>
+        <v>-1.6077</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9657</v>
+        <v>-0.0003</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4205</v>
+        <v>-1.6074</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R8" t="n">
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4767</v>
+        <v>1.9721</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6751</v>
+        <v>1.0754</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1984</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2856</v>
+        <v>0.6138</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2146</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1285</v>
+        <v>-0.0369</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0862</v>
+        <v>0.6473</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7894</v>
+        <v>-2.3369</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4622</v>
+        <v>-1.3783</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.2516</v>
+        <v>-0.9586</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8183</v>
+        <v>-1.0807</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4625</v>
+        <v>-1.4469</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6442</v>
+        <v>0.3662</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6077</v>
+        <v>-1.2563</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0003</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6074</v>
+        <v>-1.3248</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5833</v>
+        <v>1.6963</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6617</v>
+        <v>0.7582</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9215</v>
+        <v>0.9382</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6138</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6138</v>
+        <v>0.2856</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2987</v>
+        <v>0.3295</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2989</v>
+        <v>0.6361</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5976</v>
+        <v>-0.3067</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3369</v>
+        <v>-1.1363</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3783</v>
+        <v>-1.5998</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9586</v>
+        <v>0.4634</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0807</v>
+        <v>-0.5911</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4469</v>
+        <v>-0.634</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3662</v>
+        <v>0.043</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2563</v>
+        <v>-0.5453</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.9657</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3248</v>
+        <v>0.4205</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3847</v>
+        <v>0.9791</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4962</v>
+        <v>1.2272</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8885</v>
+        <v>-0.2481</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2856</v>
+        <v>-0.2856</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2543</v>
+        <v>-0.6142</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1239</v>
+        <v>-0.4341</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1304</v>
+        <v>-0.1801</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1964</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6219</v>
+        <v>1.2619</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0479</v>
+        <v>0.7376</v>
       </c>
       <c r="U11" t="n">
-        <v>0.574</v>
+        <v>0.5243</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3282</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4848</v>
+        <v>-0.7206</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7178</v>
+        <v>-1.028</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2329</v>
+        <v>0.3074</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0211</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6288</v>
+        <v>0.393</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2688</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8447</v>
+        <v>-0.7635</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2355</v>
+        <v>-0.3529</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6092</v>
+        <v>-0.4106</v>
       </c>
       <c r="G13" t="n">
         <v>-0.9192</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4468</v>
+        <v>0.6344</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4966</v>
+        <v>0.3859</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0498</v>
+        <v>0.2485</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2856</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>25.1857</v>
+        <v>25.4616</v>
       </c>
       <c r="E14" t="n">
-        <v>24.2279</v>
+        <v>24.504</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9577999999999998</v>
+        <v>0.9577</v>
       </c>
       <c r="G14" t="n">
-        <v>9.2447</v>
+        <v>9.244699999999998</v>
       </c>
       <c r="H14" t="n">
         <v>5.8648</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3796</v>
+        <v>3.379599999999999</v>
       </c>
       <c r="J14" t="n">
         <v>22.2884</v>
@@ -1531,10 +1531,10 @@
         <v>-13.0441</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.486599999999999</v>
+        <v>-4.4866</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.557199999999998</v>
+        <v>-8.557199999999996</v>
       </c>
       <c r="P14" t="n">
         <v>-0.9652999999999998</v>
@@ -1546,13 +1546,13 @@
         <v>10.6193</v>
       </c>
       <c r="S14" t="n">
-        <v>15.3082</v>
+        <v>15.5837</v>
       </c>
       <c r="T14" t="n">
-        <v>9.926400000000001</v>
+        <v>10.2021</v>
       </c>
       <c r="U14" t="n">
-        <v>5.381699999999999</v>
+        <v>5.3817</v>
       </c>
       <c r="V14" t="n">
         <v>1.5986</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1028</v>
+        <v>4.369</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0597</v>
+        <v>5.7494</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.9568</v>
+        <v>-1.3804</v>
       </c>
       <c r="G15" t="n">
         <v>4.8006</v>
@@ -1624,13 +1624,13 @@
         <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3349</v>
+        <v>-1.0687</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0279</v>
+        <v>-0.3382</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.307</v>
+        <v>-0.7306</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3282</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1495</v>
+        <v>-0.7139</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4807</v>
+        <v>1.6876</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6303</v>
+        <v>-2.4015</v>
       </c>
       <c r="G16" t="n">
         <v>3.1475</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1732</v>
+        <v>-1.7376</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9106</v>
+        <v>-0.7037</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2626</v>
+        <v>-1.0338</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. ARENAS CUESTA</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1641</v>
+        <v>-0.9638</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8453000000000001</v>
+        <v>1.4375</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3188</v>
+        <v>-2.4013</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2692</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2759</v>
+        <v>-0.1453</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0068</v>
+        <v>0.0791</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.694</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.6141</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.0799</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2692</v>
+        <v>-2.7602</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2759</v>
+        <v>-0.7594</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0068</v>
+        <v>-2.0008</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4082</v>
+        <v>-1.6619</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1655</v>
+        <v>-0.8623</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2427</v>
+        <v>-0.7995</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0.5712</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. SOTO RODRIGUEZ</t>
+          <t>J. ARENAS CUESTA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.577</v>
+        <v>-1.1144</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4366</v>
+        <v>-0.8453000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.0136</v>
+        <v>-0.2691</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4595</v>
+        <v>-0.2692</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5514</v>
+        <v>-0.2759</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9081</v>
+        <v>0.0068</v>
       </c>
       <c r="J18" t="n">
-        <v>1.397</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6215000000000001</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7754</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.8565</v>
+        <v>-0.2692</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.173</v>
+        <v>-0.2759</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.6835</v>
+        <v>0.0068</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5446</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0056</v>
+        <v>-0.3586</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4684</v>
+        <v>-0.1655</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.474</v>
+        <v>-0.193</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5712</v>
+        <v>0.2856</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>G. BERGERON</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7678</v>
+        <v>-1.6255</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3341</v>
+        <v>0.8225</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1019</v>
+        <v>-2.4481</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.2681</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1453</v>
+        <v>-0.3314</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0791</v>
+        <v>0.0633</v>
       </c>
       <c r="J19" t="n">
-        <v>2.694</v>
+        <v>1.4916</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6141</v>
+        <v>0.6348</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0799</v>
+        <v>0.8568</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7602</v>
+        <v>-1.7598</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7594</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0008</v>
+        <v>-0.7935</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.4659</v>
+        <v>-1.1378</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9657</v>
+        <v>-0.6691</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5001</v>
+        <v>-0.4686</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5712</v>
+        <v>-1.1851</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.1851</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7755</v>
+        <v>-1.7506</v>
       </c>
       <c r="E20" t="n">
         <v>0.0014</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7769</v>
+        <v>-1.752</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8017</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6455</v>
+        <v>-0.6207</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2592</v>
+        <v>-0.2344</v>
       </c>
       <c r="V20" t="n">
         <v>0.2856</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BERGERON</t>
+          <t>D. SOTO MADRIGAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0819</v>
+        <v>-2.3318</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7191</v>
+        <v>-1.4345</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.801</v>
+        <v>-0.8973</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2681</v>
+        <v>-1.5044</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3314</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0633</v>
+        <v>-1.587</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4916</v>
+        <v>-0.2896</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6348</v>
+        <v>1.0487</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8568</v>
+        <v>-1.3383</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7598</v>
+        <v>-1.2148</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.9661</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7935</v>
+        <v>-0.2487</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5941</v>
+        <v>-1.0205</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.1795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8216</v>
+        <v>-0.841</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1851</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. SOTO MADRIGAL</t>
+          <t>I. SOTO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1995</v>
+        <v>-2.5782</v>
       </c>
       <c r="E22" t="n">
+        <v>1.6092</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-4.1874</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.4595</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.5514</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.9081</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.397</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.6215000000000001</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-3.8565</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.173</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-2.6835</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.5446</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.5446</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-1.0068</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.359</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.6479</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.6565</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5712</v>
+      </c>
+      <c r="X22" t="n">
         <v>-1.2277</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.9718</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-1.5044</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.08260000000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-1.587</v>
-      </c>
-      <c r="J22" t="n">
-        <v>-0.2896</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1.0487</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-1.3383</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-1.2148</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.9661</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.2487</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.1931</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.1585</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.8882</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.0273</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.9155</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4611</v>
+        <v>-3.0804</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1939</v>
+        <v>-0.9871</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2671</v>
+        <v>-2.0933</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6568</v>
@@ -2248,13 +2248,13 @@
         <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.484</v>
+        <v>-1.1034</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6347</v>
+        <v>-0.4278</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8494</v>
+        <v>-0.6756</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2856</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.97</v>
+        <v>-4.5355</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3757</v>
+        <v>-2.0655</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5942</v>
+        <v>-2.4701</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4459</v>
@@ -2326,13 +2326,13 @@
         <v>1.3515</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8757</v>
+        <v>-1.4412</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9106</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9651</v>
+        <v>-0.8409</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.142300000000001</v>
+        <v>-8.102600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3467</v>
+        <v>-6.933</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7957</v>
+        <v>-1.1696</v>
       </c>
       <c r="G25" t="n">
         <v>-3.7209</v>
@@ -2404,13 +2404,13 @@
         <v>1.1585</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4327</v>
+        <v>-1.3929</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1036</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3291</v>
+        <v>-0.703</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2856</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-25.1859</v>
+        <v>-22.4277</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9576999999999991</v>
+        <v>-0.9578000000000007</v>
       </c>
       <c r="F26" t="n">
-        <v>-24.2281</v>
+        <v>-21.4701</v>
       </c>
       <c r="G26" t="n">
         <v>-9.2446</v>
@@ -2482,13 +2482,13 @@
         <v>11.5848</v>
       </c>
       <c r="S26" t="n">
-        <v>-15.308</v>
+        <v>-12.5501</v>
       </c>
       <c r="T26" t="n">
         <v>-5.3817</v>
       </c>
       <c r="U26" t="n">
-        <v>-9.926300000000001</v>
+        <v>-7.168300000000001</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5986</v>
